--- a/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
+++ b/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:43:29</t>
+          <t>2026-05-24 05:42:31</t>
         </is>
       </c>
     </row>

--- a/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
+++ b/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
@@ -436,7 +436,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18724</v>
+        <v>18735</v>
       </c>
     </row>
     <row r="3">
@@ -497,7 +497,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:42:31</t>
+          <t>2026-05-25 14:39:42</t>
         </is>
       </c>
     </row>

--- a/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
+++ b/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:39:42</t>
+          <t>2026-05-26 14:28:32</t>
         </is>
       </c>
     </row>

--- a/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
+++ b/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:28:32</t>
+          <t>2026-05-27 15:03:48</t>
         </is>
       </c>
     </row>

--- a/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
+++ b/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-27 15:03:48</t>
+          <t>2026-05-28 08:59:36</t>
         </is>
       </c>
     </row>

--- a/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
+++ b/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:59:36</t>
+          <t>2026-05-28 17:27:54</t>
         </is>
       </c>
     </row>

--- a/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
+++ b/data/football/processed/features/football_features_tier2_europe/feature_summary.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:27:54</t>
+          <t>2026-05-28 19:55:03</t>
         </is>
       </c>
     </row>
